--- a/exports/RELIANCE_full_report.xlsx
+++ b/exports/RELIANCE_full_report.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q86"/>
+  <dimension ref="A1:Q87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="C86" s="1" t="n">
@@ -5321,13 +5321,21 @@
       <c r="F86" t="n">
         <v>5.62</v>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" s="1" t="n">
+        <v>46322.55208333334</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1202.1</v>
+      </c>
       <c r="I86" t="n">
         <v>1167.901744850155</v>
       </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="J86" s="2" t="n">
+        <v>12.16666666666667</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-0.75</v>
+      </c>
       <c r="L86" t="n">
         <v>3.97</v>
       </c>
@@ -5345,6 +5353,55 @@
       </c>
       <c r="Q86" t="n">
         <v>16</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>46323.38541666666</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1167.7</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1245.084632222485</v>
+      </c>
+      <c r="F87" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="n">
+        <v>1219.606169000236</v>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="P87" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -7367,16 +7424,16 @@
         <v>1152.2</v>
       </c>
       <c r="E59" t="n">
-        <v>1190.3</v>
+        <v>1160</v>
       </c>
       <c r="F59" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G59" t="n">
         <v>6.96</v>
       </c>
       <c r="H59" t="n">
-        <v>0.86</v>
+        <v>-1.7</v>
       </c>
       <c r="I59" t="n">
         <v>4.59</v>
@@ -7418,7 +7475,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
@@ -7428,7 +7485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -7448,7 +7505,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="6">
@@ -7488,7 +7545,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -7508,7 +7565,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12">
@@ -7528,7 +7585,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>78.59999999999999</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="14">
@@ -7538,7 +7595,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="15">
@@ -7548,7 +7605,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="16">
@@ -7578,7 +7635,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42.9</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="19">
@@ -7588,7 +7645,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="20">
@@ -7658,7 +7715,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="27">

--- a/exports/RELIANCE_full_report.xlsx
+++ b/exports/RELIANCE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:U87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>3.77</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1180.05</v>
+        <v>1153.1</v>
       </c>
       <c r="I2" t="n">
         <v>1175.482715841791</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>1.91</v>
+        <v>-0.41</v>
       </c>
       <c r="L2" t="n">
-        <v>0.55</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>1.32</v>
       </c>
       <c r="N2" t="n">
-        <v>1.52</v>
+        <v>3.92</v>
       </c>
       <c r="O2" t="n">
         <v>0.01</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6.55</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44608.55208333334</v>
+        <v>44609.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>1147.5</v>
+        <v>1167.2</v>
       </c>
       <c r="I3" t="n">
         <v>1156.323579807347</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>0.49</v>
+        <v>-1.22</v>
       </c>
       <c r="L3" t="n">
         <v>3.49</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>5.17</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44615.55208333334</v>
+        <v>44616.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>1130.15</v>
+        <v>1097.3</v>
       </c>
       <c r="I4" t="n">
         <v>1116.510734159885</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.17</v>
+        <v>-5.99</v>
       </c>
       <c r="L4" t="n">
-        <v>4.14</v>
+        <v>7.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.95</v>
+        <v>2.79</v>
       </c>
       <c r="N4" t="n">
-        <v>1.14</v>
+        <v>5.04</v>
       </c>
       <c r="O4" t="n">
         <v>1.42</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>5.6</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1123.8</v>
+        <v>1138.2</v>
       </c>
       <c r="I5" t="n">
         <v>1123.852524949981</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.42</v>
+        <v>-3.73</v>
       </c>
       <c r="L5" t="n">
         <v>4.88</v>
       </c>
       <c r="M5" t="n">
-        <v>1.26</v>
+        <v>1.78</v>
       </c>
       <c r="N5" t="n">
         <v>5.5</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>6.71</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44663.38541666666</v>
+        <v>44663.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>1221</v>
+        <v>1220.1</v>
       </c>
       <c r="I6" t="n">
         <v>1220.926827686378</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K6" t="n">
-        <v>7.27</v>
+        <v>7.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.92</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>4.32</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44670.55208333334</v>
+        <v>44671.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>1251.55</v>
+        <v>1294.4</v>
       </c>
       <c r="I7" t="n">
         <v>1259.769618300603</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.58</v>
+        <v>-6.09</v>
       </c>
       <c r="L7" t="n">
-        <v>4.22</v>
+        <v>6.68</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7</v>
+        <v>1.19</v>
       </c>
       <c r="N7" t="n">
-        <v>3.38</v>
+        <v>3.47</v>
       </c>
       <c r="O7" t="n">
         <v>-1.95</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.27</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44685.55208333334</v>
+        <v>44686.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>1283</v>
+        <v>1273</v>
       </c>
       <c r="I8" t="n">
         <v>1280.97015581567</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.88</v>
+        <v>-1.65</v>
       </c>
       <c r="L8" t="n">
         <v>2.43</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>7.07</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44700.55208333334</v>
+        <v>44701.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1179.8</v>
+        <v>1221.85</v>
       </c>
       <c r="I9" t="n">
         <v>1216.695394191204</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
-        <v>7.32</v>
+        <v>4.02</v>
       </c>
       <c r="L9" t="n">
         <v>2.21</v>
       </c>
       <c r="M9" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="N9" t="n">
-        <v>4.41</v>
+        <v>6.2</v>
       </c>
       <c r="O9" t="n">
         <v>-1.78</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.68</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44725.55208333334</v>
+        <v>44726.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1271.6</v>
+        <v>1253.9</v>
       </c>
       <c r="I10" t="n">
         <v>1258.651700584945</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K10" t="n">
-        <v>4.07</v>
+        <v>2.62</v>
       </c>
       <c r="L10" t="n">
         <v>2.33</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.39</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44763.55208333334</v>
+        <v>44764.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1185.3</v>
+        <v>1194.65</v>
       </c>
       <c r="I11" t="n">
         <v>1192.133950749451</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K11" t="n">
-        <v>5.47</v>
+        <v>4.73</v>
       </c>
       <c r="L11" t="n">
         <v>1.52</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,25 +1247,25 @@
         <v>4.37</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44803.55208333334</v>
+        <v>44805.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1259.2</v>
+        <v>1226.3</v>
       </c>
       <c r="I12" t="n">
         <v>1231.833536925501</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K12" t="n">
-        <v>5.4</v>
+        <v>2.65</v>
       </c>
       <c r="L12" t="n">
         <v>4.17</v>
       </c>
       <c r="M12" t="n">
-        <v>1.45</v>
+        <v>2.25</v>
       </c>
       <c r="N12" t="n">
         <v>3.42</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>5.2</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1150</v>
+        <v>1159.5</v>
       </c>
       <c r="I13" t="n">
         <v>1157.350884572247</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K13" t="n">
-        <v>6.22</v>
+        <v>5.45</v>
       </c>
       <c r="L13" t="n">
         <v>2.19</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>4.24</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44902.38541666666</v>
+        <v>44902.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>1272.05</v>
+        <v>1261.55</v>
       </c>
       <c r="I14" t="n">
         <v>1262.483269739759</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>62</v>
+        <v>62.16666666666666</v>
       </c>
       <c r="K14" t="n">
-        <v>9.710000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L14" t="n">
         <v>3.67</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>3.87</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44935.38541666666</v>
+        <v>44935.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>1233.6</v>
+        <v>1236.3</v>
       </c>
       <c r="I15" t="n">
         <v>1234.872150340801</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>32.83333333333334</v>
+        <v>33</v>
       </c>
       <c r="K15" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>0.95</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>3.59</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44937.55208333334</v>
+        <v>44938.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1203.35</v>
+        <v>1181.3</v>
       </c>
       <c r="I16" t="n">
         <v>1191.858537161401</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.67</v>
+        <v>-4.45</v>
       </c>
       <c r="L16" t="n">
-        <v>2.81</v>
+        <v>4.65</v>
       </c>
       <c r="M16" t="n">
         <v>0.37</v>
       </c>
       <c r="N16" t="n">
-        <v>1.45</v>
+        <v>1.97</v>
       </c>
       <c r="O16" t="n">
         <v>2.25</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>4.85</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44971.55208333334</v>
+        <v>44972.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>1134.3</v>
+        <v>1153.1</v>
       </c>
       <c r="I17" t="n">
         <v>1138.368420339862</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K17" t="n">
-        <v>3.98</v>
+        <v>2.39</v>
       </c>
       <c r="L17" t="n">
         <v>2.18</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>4.43</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44981.55208333334</v>
+        <v>44984.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1138.1</v>
+        <v>1124</v>
       </c>
       <c r="I18" t="n">
         <v>1125.66235742679</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3</v>
+        <v>-2.52</v>
       </c>
       <c r="L18" t="n">
-        <v>2.39</v>
+        <v>2.71</v>
       </c>
       <c r="M18" t="n">
         <v>0.41</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>4.09</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44988.55208333334</v>
+        <v>44991.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>1135.25</v>
+        <v>1153.65</v>
       </c>
       <c r="I19" t="n">
         <v>1144.618360890817</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K19" t="n">
-        <v>-1</v>
+        <v>-2.64</v>
       </c>
       <c r="L19" t="n">
-        <v>1.49</v>
+        <v>2.7</v>
       </c>
       <c r="M19" t="n">
         <v>1.04</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>3.84</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44994.55208333334</v>
+        <v>44995.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1124.8</v>
+        <v>1106.05</v>
       </c>
       <c r="I20" t="n">
         <v>1112.439163419535</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.5</v>
+        <v>-4.13</v>
       </c>
       <c r="L20" t="n">
-        <v>2.7</v>
+        <v>4.36</v>
       </c>
       <c r="M20" t="n">
-        <v>0.03</v>
+        <v>0.79</v>
       </c>
       <c r="N20" t="n">
         <v>2.34</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>4.06</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45014.55208333334</v>
+        <v>45016.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1069</v>
+        <v>1107.9</v>
       </c>
       <c r="I21" t="n">
         <v>1093.628237481209</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K21" t="n">
-        <v>3.35</v>
+        <v>-0.17</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
@@ -1638,7 +1889,7 @@
         <v>0.68</v>
       </c>
       <c r="N21" t="n">
-        <v>2.74</v>
+        <v>3.86</v>
       </c>
       <c r="O21" t="n">
         <v>-1.44</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.75</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45064.38541666666</v>
+        <v>45064.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>1163.6</v>
+        <v>1159.6</v>
       </c>
       <c r="I22" t="n">
         <v>1161.237338247651</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K22" t="n">
-        <v>5.03</v>
+        <v>4.67</v>
       </c>
       <c r="L22" t="n">
         <v>3</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>2.93</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45072.38541666666</v>
+        <v>45072.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>1185.75</v>
+        <v>1195.55</v>
       </c>
       <c r="I23" t="n">
         <v>1186.021216695961</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.26</v>
+        <v>-3.1</v>
       </c>
       <c r="L23" t="n">
-        <v>2.48</v>
+        <v>3.12</v>
       </c>
       <c r="M23" t="n">
         <v>0.54</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>3.27</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45079.38541666666</v>
+        <v>45079.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>1173</v>
+        <v>1170.2</v>
       </c>
       <c r="I24" t="n">
         <v>1171.748803425093</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.89</v>
+        <v>-2.12</v>
       </c>
       <c r="L24" t="n">
         <v>2.29</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>3.17</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45090.55208333334</v>
+        <v>45091.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1199.6</v>
+        <v>1216.5</v>
       </c>
       <c r="I25" t="n">
         <v>1207.351411883965</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.51</v>
+        <v>-3.96</v>
       </c>
       <c r="L25" t="n">
-        <v>2.78</v>
+        <v>3.98</v>
       </c>
       <c r="M25" t="n">
         <v>0.49</v>
       </c>
       <c r="N25" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="O25" t="n">
         <v>-0.48</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>3.34</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45100.55208333334</v>
+        <v>45103.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1200</v>
+        <v>1188.9</v>
       </c>
       <c r="I26" t="n">
         <v>1196.073828827206</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.36</v>
+        <v>-2.27</v>
       </c>
       <c r="L26" t="n">
-        <v>1.58</v>
+        <v>2.48</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="N26" t="n">
         <v>1.01</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>2.86</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45107.38541666666</v>
+        <v>45107.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>1211.35</v>
+        <v>1216.9</v>
       </c>
       <c r="I27" t="n">
         <v>1215.350286985758</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.89</v>
+        <v>-2.36</v>
       </c>
       <c r="L27" t="n">
-        <v>2.08</v>
+        <v>2.49</v>
       </c>
       <c r="M27" t="n">
         <v>0.72</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>2.71</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45127.55208333334</v>
+        <v>45128.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1312</v>
+        <v>1266.4</v>
       </c>
       <c r="I28" t="n">
         <v>1291.0685109912</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>7.81</v>
+        <v>4.07</v>
       </c>
       <c r="L28" t="n">
         <v>0.78</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>7.33</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45152.38541666666</v>
+        <v>45152.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>1280.6</v>
+        <v>1286.6</v>
       </c>
       <c r="I29" t="n">
         <v>1284.894910659991</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.12</v>
+        <v>-1.6</v>
       </c>
       <c r="L29" t="n">
         <v>3.24</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>3.61</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45162.38541666666</v>
+        <v>45162.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>1248.5</v>
+        <v>1237.9</v>
       </c>
       <c r="I30" t="n">
         <v>1242.507535785056</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.96</v>
+        <v>-3.79</v>
       </c>
       <c r="L30" t="n">
-        <v>3.02</v>
+        <v>3.97</v>
       </c>
       <c r="M30" t="n">
         <v>0.86</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>4.28</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45216.38541666666</v>
+        <v>45216.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>1175</v>
+        <v>1178.5</v>
       </c>
       <c r="I31" t="n">
         <v>1177.073209195149</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>53.83333333333334</v>
+        <v>54</v>
       </c>
       <c r="K31" t="n">
-        <v>5.08</v>
+        <v>4.8</v>
       </c>
       <c r="L31" t="n">
         <v>1.32</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>2.45</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45219.38541666666</v>
+        <v>45219.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>1149.7</v>
+        <v>1148.3</v>
       </c>
       <c r="I32" t="n">
         <v>1149.635017071918</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.44</v>
+        <v>-2.56</v>
       </c>
       <c r="L32" t="n">
         <v>2.58</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>2.43</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45226.55208333334</v>
+        <v>45229.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1132</v>
+        <v>1160.5</v>
       </c>
       <c r="I33" t="n">
         <v>1145.242940618965</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K33" t="n">
-        <v>1.42</v>
+        <v>-1.06</v>
       </c>
       <c r="L33" t="n">
-        <v>0.42</v>
+        <v>1.24</v>
       </c>
       <c r="M33" t="n">
         <v>0.72</v>
       </c>
       <c r="N33" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="O33" t="n">
         <v>-0.28</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>4.45</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1359</v>
+        <v>1328.75</v>
       </c>
       <c r="I34" t="n">
         <v>1341.570584099733</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>82.16666666666667</v>
+        <v>85</v>
       </c>
       <c r="K34" t="n">
-        <v>17.1</v>
+        <v>14.5</v>
       </c>
       <c r="L34" t="n">
         <v>2.2</v>
@@ -2379,7 +2786,7 @@
         <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>1.46</v>
+        <v>2.25</v>
       </c>
       <c r="O34" t="n">
         <v>1.99</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>6.09</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45316.55208333334</v>
+        <v>45320.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1355.5</v>
+        <v>1430</v>
       </c>
       <c r="I35" t="n">
         <v>1385.841102738562</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.01</v>
+        <v>-7.62</v>
       </c>
       <c r="L35" t="n">
-        <v>3.24</v>
+        <v>7.72</v>
       </c>
       <c r="M35" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>1.43</v>
+        <v>6.68</v>
       </c>
       <c r="O35" t="n">
         <v>-2.25</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.53</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>1454.7</v>
+        <v>1437</v>
       </c>
       <c r="I36" t="n">
         <v>1451.115315403676</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K36" t="n">
-        <v>1.73</v>
+        <v>0.49</v>
       </c>
       <c r="L36" t="n">
         <v>4.88</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>4.6</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45377.55208333334</v>
+        <v>45378.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1443.35</v>
+        <v>1493</v>
       </c>
       <c r="I37" t="n">
         <v>1475.225169875819</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.44</v>
+        <v>-3.9</v>
       </c>
       <c r="L37" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="M37" t="n">
         <v>0.65</v>
       </c>
       <c r="N37" t="n">
-        <v>1.3</v>
+        <v>3.44</v>
       </c>
       <c r="O37" t="n">
         <v>-2.69</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>4.99</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45414.55208333334</v>
+        <v>45415.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1469.05</v>
+        <v>1426.6</v>
       </c>
       <c r="I38" t="n">
         <v>1446.874425944124</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.6</v>
+        <v>-4.45</v>
       </c>
       <c r="L38" t="n">
-        <v>3.45</v>
+        <v>4.62</v>
       </c>
       <c r="M38" t="n">
         <v>0.83</v>
       </c>
       <c r="N38" t="n">
-        <v>1.38</v>
+        <v>2.28</v>
       </c>
       <c r="O38" t="n">
         <v>3.44</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>5.45</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45433.55208333334</v>
+        <v>45434.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1434</v>
+        <v>1464.8</v>
       </c>
       <c r="I39" t="n">
         <v>1452.712766086854</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.52</v>
+        <v>-2.68</v>
       </c>
       <c r="L39" t="n">
         <v>3.39</v>
@@ -2664,7 +3131,7 @@
         <v>0.31</v>
       </c>
       <c r="N39" t="n">
-        <v>1.21</v>
+        <v>1.81</v>
       </c>
       <c r="O39" t="n">
         <v>-2.28</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>4.43</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45441.55208333334</v>
+        <v>45442.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1440.5</v>
+        <v>1428.5</v>
       </c>
       <c r="I40" t="n">
         <v>1433.685829943355</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.66</v>
+        <v>-2.48</v>
       </c>
       <c r="L40" t="n">
-        <v>1.95</v>
+        <v>2.79</v>
       </c>
       <c r="M40" t="n">
         <v>0.62</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>3.5</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1429.5</v>
+        <v>1487.25</v>
       </c>
       <c r="I41" t="n">
         <v>1471.336101363</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-4.11</v>
       </c>
       <c r="L41" t="n">
-        <v>0.96</v>
+        <v>4.48</v>
       </c>
       <c r="M41" t="n">
-        <v>0.12</v>
+        <v>3.74</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="O41" t="n">
         <v>-0.76</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>4.83</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1514</v>
+        <v>1403.9</v>
       </c>
       <c r="I42" t="n">
         <v>1437.396188895736</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1.8</v>
+        <v>-5.6</v>
       </c>
       <c r="L42" t="n">
-        <v>1.9</v>
+        <v>8.6</v>
       </c>
       <c r="M42" t="n">
-        <v>0.01</v>
+        <v>1.05</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>6.46</v>
       </c>
       <c r="O42" t="n">
         <v>5.91</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>9.1</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45469.38541666666</v>
+        <v>45469.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1490.8</v>
+        <v>1510.5</v>
       </c>
       <c r="I43" t="n">
         <v>1498.875509016011</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.19</v>
+        <v>-7.59</v>
       </c>
       <c r="L43" t="n">
-        <v>6.71</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M43" t="n">
         <v>1.13</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>4.7</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45492.55208333334</v>
+        <v>45495.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1558.5</v>
+        <v>1502.85</v>
       </c>
       <c r="I44" t="n">
         <v>1541.796778830109</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>23</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>3.18</v>
+        <v>-0.51</v>
       </c>
       <c r="L44" t="n">
         <v>1.39</v>
       </c>
       <c r="M44" t="n">
-        <v>0.34</v>
+        <v>1.36</v>
       </c>
       <c r="N44" t="n">
-        <v>1.69</v>
+        <v>3.61</v>
       </c>
       <c r="O44" t="n">
         <v>3.99</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.88</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45523.55208333334</v>
+        <v>45524.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1489.5</v>
+        <v>1502.6</v>
       </c>
       <c r="I45" t="n">
         <v>1499.278830767075</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K45" t="n">
-        <v>0.89</v>
+        <v>0.02</v>
       </c>
       <c r="L45" t="n">
         <v>2.31</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>3.2</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45540.55208333334</v>
+        <v>45541.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1495.5</v>
+        <v>1466.05</v>
       </c>
       <c r="I46" t="n">
         <v>1474.584610960793</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.47</v>
+        <v>-2.43</v>
       </c>
       <c r="L46" t="n">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="M46" t="n">
         <v>0.58</v>
       </c>
       <c r="N46" t="n">
-        <v>1.35</v>
+        <v>2.01</v>
       </c>
       <c r="O46" t="n">
         <v>0.27</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>4.51</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45555.55208333334</v>
+        <v>45558.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1485</v>
+        <v>1496.65</v>
       </c>
       <c r="I47" t="n">
         <v>1496.143991223348</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.29</v>
+        <v>-2.09</v>
       </c>
       <c r="L47" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="M47" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="N47" t="n">
         <v>1.69</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>3.17</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45565.55208333334</v>
+        <v>45566.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1479</v>
+        <v>1466.5</v>
       </c>
       <c r="I48" t="n">
         <v>1469.285172026186</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.18</v>
+        <v>-2.01</v>
       </c>
       <c r="L48" t="n">
-        <v>1.49</v>
+        <v>2.24</v>
       </c>
       <c r="M48" t="n">
         <v>0.43</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,25 +3800,25 @@
         <v>4.26</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1264</v>
+        <v>1289.15</v>
       </c>
       <c r="I49" t="n">
         <v>1276.600943346796</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K49" t="n">
-        <v>13.81</v>
+        <v>12.09</v>
       </c>
       <c r="L49" t="n">
         <v>1.46</v>
       </c>
       <c r="M49" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.06</v>
       </c>
       <c r="N49" t="n">
         <v>3.57</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>4.72</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45637.55208333334</v>
+        <v>45638.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1279</v>
+        <v>1265.7</v>
       </c>
       <c r="I50" t="n">
         <v>1271.673331834322</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.79</v>
+        <v>-1.82</v>
       </c>
       <c r="L50" t="n">
-        <v>1.56</v>
+        <v>2.18</v>
       </c>
       <c r="M50" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="N50" t="n">
         <v>1.65</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>3.5</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45659.55208333334</v>
+        <v>45660.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1240.8</v>
+        <v>1259.1</v>
       </c>
       <c r="I51" t="n">
         <v>1246.08112058575</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K51" t="n">
-        <v>1.97</v>
+        <v>0.52</v>
       </c>
       <c r="L51" t="n">
         <v>1.21</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>3.93</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45663.38541666666</v>
+        <v>45663.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>1230.35</v>
+        <v>1216.25</v>
       </c>
       <c r="I52" t="n">
         <v>1216.77048731031</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.28</v>
+        <v>-3.4</v>
       </c>
       <c r="L52" t="n">
-        <v>2.81</v>
+        <v>3.5</v>
       </c>
       <c r="M52" t="n">
         <v>-0</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>4.44</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45673.38541666666</v>
+        <v>45673.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>1260.55</v>
+        <v>1273.7</v>
       </c>
       <c r="I53" t="n">
         <v>1270.198655278649</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.64</v>
+        <v>-4.72</v>
       </c>
       <c r="L53" t="n">
-        <v>4.51</v>
+        <v>4.83</v>
       </c>
       <c r="M53" t="n">
         <v>0.73</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>4.07</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45680.55208333334</v>
+        <v>45681.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1264.9</v>
+        <v>1254.45</v>
       </c>
       <c r="I54" t="n">
         <v>1255.697971912385</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.51</v>
       </c>
       <c r="L54" t="n">
-        <v>1.06</v>
+        <v>1.77</v>
       </c>
       <c r="M54" t="n">
         <v>0.65</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>4.52</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45692.38541666666</v>
+        <v>45692.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>1276.2</v>
+        <v>1282.9</v>
       </c>
       <c r="I55" t="n">
         <v>1278.919930698221</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.73</v>
+        <v>-2.27</v>
       </c>
       <c r="L55" t="n">
-        <v>1.84</v>
+        <v>2.74</v>
       </c>
       <c r="M55" t="n">
         <v>0.73</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>4.26</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45699.55208333334</v>
+        <v>45700.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1237.55</v>
+        <v>1217.3</v>
       </c>
       <c r="I56" t="n">
         <v>1232.900993460791</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.53</v>
+        <v>-5.11</v>
       </c>
       <c r="L56" t="n">
-        <v>4.12</v>
+        <v>6.98</v>
       </c>
       <c r="M56" t="n">
-        <v>0.53</v>
+        <v>1.46</v>
       </c>
       <c r="N56" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="O56" t="n">
         <v>2.88</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>4.04</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45722.55208333334</v>
+        <v>45723.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1210.5</v>
+        <v>1247.95</v>
       </c>
       <c r="I57" t="n">
         <v>1210.564316983419</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5600000000000001</v>
+        <v>-2.52</v>
       </c>
       <c r="L57" t="n">
-        <v>1.86</v>
+        <v>3.06</v>
       </c>
       <c r="M57" t="n">
         <v>1.69</v>
       </c>
       <c r="N57" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="O57" t="n">
         <v>-1.66</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>5.74</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45744.55208333334</v>
+        <v>45748.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1274</v>
+        <v>1258.15</v>
       </c>
       <c r="I58" t="n">
         <v>1261.619819177429</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K58" t="n">
-        <v>2.09</v>
+        <v>0.82</v>
       </c>
       <c r="L58" t="n">
         <v>2.88</v>
       </c>
       <c r="M58" t="n">
-        <v>0.36</v>
+        <v>0.74</v>
       </c>
       <c r="N58" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="O58" t="n">
         <v>2.95</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>4.48</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45756.55208333334</v>
+        <v>45758.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1187.55</v>
+        <v>1219.95</v>
       </c>
       <c r="I59" t="n">
         <v>1212.471910187288</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K59" t="n">
-        <v>5.61</v>
+        <v>3.04</v>
       </c>
       <c r="L59" t="n">
         <v>1.57</v>
       </c>
       <c r="M59" t="n">
-        <v>0.08</v>
+        <v>0.64</v>
       </c>
       <c r="N59" t="n">
-        <v>0.86</v>
+        <v>2.73</v>
       </c>
       <c r="O59" t="n">
         <v>-1.57</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.9</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1515.2</v>
+        <v>1492.9</v>
       </c>
       <c r="I60" t="n">
         <v>1497.807072445847</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>90.16666666666667</v>
+        <v>91</v>
       </c>
       <c r="K60" t="n">
-        <v>24.2</v>
+        <v>22.37</v>
       </c>
       <c r="L60" t="n">
         <v>2.03</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>4.12</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45888.38541666666</v>
+        <v>45888.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>1413.6</v>
+        <v>1421</v>
       </c>
       <c r="I61" t="n">
         <v>1418.466277608923</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K61" t="n">
-        <v>5.31</v>
+        <v>4.82</v>
       </c>
       <c r="L61" t="n">
         <v>1.48</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>3.6</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45895.55208333334</v>
+        <v>45897.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1383.8</v>
+        <v>1376.5</v>
       </c>
       <c r="I62" t="n">
         <v>1380.252808281601</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>7</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.62</v>
+        <v>-3.13</v>
       </c>
       <c r="L62" t="n">
-        <v>2.77</v>
+        <v>3.84</v>
       </c>
       <c r="M62" t="n">
         <v>0.5600000000000001</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>3.47</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45916.55208333334</v>
+        <v>45917.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1405.9</v>
+        <v>1412.3</v>
       </c>
       <c r="I63" t="n">
         <v>1407.853607418309</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.14</v>
+        <v>-2.6</v>
       </c>
       <c r="L63" t="n">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="M63" t="n">
         <v>0.51</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>2.31</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45922.55208333334</v>
+        <v>45923.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1390.9</v>
+        <v>1385.4</v>
       </c>
       <c r="I64" t="n">
         <v>1386.533921534659</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.52</v>
+        <v>-1.9</v>
       </c>
       <c r="L64" t="n">
-        <v>1.72</v>
+        <v>2.51</v>
       </c>
       <c r="M64" t="n">
         <v>0.26</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>2.41</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45946.38541666666</v>
+        <v>45946.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>1383.1</v>
+        <v>1398.5</v>
       </c>
       <c r="I65" t="n">
         <v>1395.426343795094</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K65" t="n">
-        <v>0.17</v>
+        <v>-0.95</v>
       </c>
       <c r="L65" t="n">
-        <v>0.77</v>
+        <v>1.09</v>
       </c>
       <c r="M65" t="n">
         <v>0.59</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>3.15</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45995.38541666666</v>
+        <v>45995.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>1546</v>
+        <v>1525.9</v>
       </c>
       <c r="I66" t="n">
         <v>1529.510648772063</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>48.83333333333334</v>
+        <v>49</v>
       </c>
       <c r="K66" t="n">
-        <v>10.55</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="L66" t="n">
         <v>1.31</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>3.82</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46022.55208333334</v>
+        <v>46023.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1570.5</v>
+        <v>1575.2</v>
       </c>
       <c r="I67" t="n">
         <v>1575.032990909967</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.92</v>
+        <v>-3.23</v>
       </c>
       <c r="L67" t="n">
-        <v>3.6</v>
+        <v>4.36</v>
       </c>
       <c r="M67" t="n">
         <v>0.71</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>2.15</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46027.55208333334</v>
+        <v>46028.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1577.2</v>
+        <v>1506</v>
       </c>
       <c r="I68" t="n">
         <v>1557.443036290035</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K68" t="n">
-        <v>0.13</v>
+        <v>-4.39</v>
       </c>
       <c r="L68" t="n">
-        <v>0.26</v>
+        <v>5.01</v>
       </c>
       <c r="M68" t="n">
-        <v>0.03</v>
+        <v>0.52</v>
       </c>
       <c r="N68" t="n">
-        <v>0.99</v>
+        <v>4.34</v>
       </c>
       <c r="O68" t="n">
         <v>0.14</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>5.91</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>1387.5</v>
+        <v>1442.8</v>
       </c>
       <c r="I69" t="n">
         <v>1433.687605136079</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K69" t="n">
-        <v>7.87</v>
+        <v>4.2</v>
       </c>
       <c r="L69" t="n">
         <v>4.18</v>
       </c>
       <c r="M69" t="n">
-        <v>0.31</v>
+        <v>6.23</v>
       </c>
       <c r="N69" t="n">
-        <v>3.31</v>
+        <v>3.64</v>
       </c>
       <c r="O69" t="n">
         <v>-4.34</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>5.71</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46072.38541666666</v>
+        <v>46072.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>1418.3</v>
+        <v>1407.3</v>
       </c>
       <c r="I70" t="n">
         <v>1412.443964087464</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.7</v>
+        <v>-2.46</v>
       </c>
       <c r="L70" t="n">
-        <v>2.32</v>
+        <v>2.97</v>
       </c>
       <c r="M70" t="n">
         <v>0.33</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,25 +5318,25 @@
         <v>4.08</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46086.55208333334</v>
+        <v>46087.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>1386.4</v>
+        <v>1418.1</v>
       </c>
       <c r="I71" t="n">
         <v>1398.592152802154</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K71" t="n">
-        <v>1.49</v>
+        <v>-0.77</v>
       </c>
       <c r="L71" t="n">
         <v>2.36</v>
       </c>
       <c r="M71" t="n">
-        <v>0.58</v>
+        <v>0.73</v>
       </c>
       <c r="N71" t="n">
         <v>3.06</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>6.32</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46106.55208333334</v>
+        <v>46108.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>1413.8</v>
+        <v>1351.6</v>
       </c>
       <c r="I72" t="n">
         <v>1362.015884363449</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.3</v>
+        <v>-4.69</v>
       </c>
       <c r="L72" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="M72" t="n">
         <v>2.27</v>
       </c>
       <c r="N72" t="n">
-        <v>1.69</v>
+        <v>4.65</v>
       </c>
       <c r="O72" t="n">
         <v>1.49</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>7.27</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46139.55208333334</v>
+        <v>46140.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>1370.5</v>
+        <v>1379</v>
       </c>
       <c r="I73" t="n">
         <v>1373.039798020367</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.4</v>
+        <v>-2.03</v>
       </c>
       <c r="L73" t="n">
         <v>3.93</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>4.85</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46153.38541666666</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="H74" t="n">
-        <v>1401.7</v>
+        <v>1385.3</v>
       </c>
       <c r="I74" t="n">
         <v>1399.360215420479</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K74" t="n">
-        <v>1.65</v>
+        <v>0.46</v>
       </c>
       <c r="L74" t="n">
         <v>1.6</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>5.47</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46188.55208333334</v>
+        <v>46189.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>1306.5</v>
+        <v>1331.9</v>
       </c>
       <c r="I75" t="n">
         <v>1312.581974218996</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K75" t="n">
-        <v>5.69</v>
+        <v>3.85</v>
       </c>
       <c r="L75" t="n">
         <v>1.31</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>5.28</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H76" t="n">
-        <v>1290.1</v>
+        <v>1274.9</v>
       </c>
       <c r="I76" t="n">
         <v>1282.349033750333</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K76" t="n">
-        <v>-3.14</v>
+        <v>-4.28</v>
       </c>
       <c r="L76" t="n">
-        <v>4.09</v>
+        <v>4.53</v>
       </c>
       <c r="M76" t="n">
         <v>0.65</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>4.17</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46220.38541666666</v>
+        <v>46220.55208333334</v>
       </c>
       <c r="H77" t="n">
-        <v>1321</v>
+        <v>1329</v>
       </c>
       <c r="I77" t="n">
         <v>1328.085288956407</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K77" t="n">
-        <v>-3.62</v>
+        <v>-4.24</v>
       </c>
       <c r="L77" t="n">
-        <v>3.83</v>
+        <v>4.35</v>
       </c>
       <c r="M77" t="n">
         <v>0.9</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,22 +5801,22 @@
         <v>3.92</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46225.55208333334</v>
+        <v>46226.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>1283.6</v>
+        <v>1275.3</v>
       </c>
       <c r="I78" t="n">
         <v>1279.24413150314</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K78" t="n">
-        <v>-3.42</v>
+        <v>-4.04</v>
       </c>
       <c r="L78" t="n">
-        <v>3.63</v>
+        <v>4.1</v>
       </c>
       <c r="M78" t="n">
         <v>0.89</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4923,28 +5870,28 @@
         <v>4.08</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46239.55208333334</v>
+        <v>46240.38541666666</v>
       </c>
       <c r="H79" t="n">
-        <v>1280</v>
+        <v>1320.8</v>
       </c>
       <c r="I79" t="n">
         <v>1309.359511593798</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.37</v>
+        <v>-3.57</v>
       </c>
       <c r="L79" t="n">
-        <v>3.18</v>
+        <v>3.91</v>
       </c>
       <c r="M79" t="n">
         <v>0.78</v>
       </c>
       <c r="N79" t="n">
-        <v>1.21</v>
+        <v>3.27</v>
       </c>
       <c r="O79" t="n">
         <v>-0.86</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,22 +5939,22 @@
         <v>5.1</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46261.55208333334</v>
+        <v>46262.38541666666</v>
       </c>
       <c r="H80" t="n">
-        <v>1288.1</v>
+        <v>1283.1</v>
       </c>
       <c r="I80" t="n">
         <v>1284.440760834719</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K80" t="n">
-        <v>-2.48</v>
+        <v>-2.85</v>
       </c>
       <c r="L80" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="M80" t="n">
         <v>0.45</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>2.8</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46267.38541666666</v>
+        <v>46267.55208333334</v>
       </c>
       <c r="H81" t="n">
-        <v>1309.1</v>
+        <v>1313.8</v>
       </c>
       <c r="I81" t="n">
         <v>1312.86373209889</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K81" t="n">
-        <v>-2.03</v>
+        <v>-2.39</v>
       </c>
       <c r="L81" t="n">
         <v>3.02</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S81" t="b">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>3.15</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46274.38541666666</v>
+        <v>46274.55208333334</v>
       </c>
       <c r="H82" t="n">
-        <v>1287.6</v>
+        <v>1285.6</v>
       </c>
       <c r="I82" t="n">
         <v>1287.455308044483</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K82" t="n">
-        <v>-1.99</v>
+        <v>-2.15</v>
       </c>
       <c r="L82" t="n">
         <v>2.79</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S82" t="b">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -5151,19 +6146,19 @@
         <v>3.17</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H83" t="n">
-        <v>1188.7</v>
+        <v>1214.9</v>
       </c>
       <c r="I83" t="n">
         <v>1205.580906306584</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K83" t="n">
-        <v>7.54</v>
+        <v>5.5</v>
       </c>
       <c r="L83" t="n">
         <v>0.39</v>
@@ -5172,7 +6167,7 @@
         <v>0.32</v>
       </c>
       <c r="N83" t="n">
-        <v>1.59</v>
+        <v>2.3</v>
       </c>
       <c r="O83" t="n">
         <v>-0.5</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5208,22 +6215,22 @@
         <v>4.55</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46304.55208333334</v>
+        <v>46307.38541666666</v>
       </c>
       <c r="H84" t="n">
-        <v>1170.9</v>
+        <v>1156.5</v>
       </c>
       <c r="I84" t="n">
         <v>1170.78730737225</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K84" t="n">
-        <v>-3.62</v>
+        <v>-4.81</v>
       </c>
       <c r="L84" t="n">
-        <v>4.5</v>
+        <v>4.92</v>
       </c>
       <c r="M84" t="n">
         <v>0.33</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S84" t="b">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5265,28 +6284,28 @@
         <v>5.32</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46309.55208333334</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="H85" t="n">
-        <v>1178.4</v>
+        <v>1211.2</v>
       </c>
       <c r="I85" t="n">
         <v>1201.108047785056</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K85" t="n">
-        <v>-1.89</v>
+        <v>-4.73</v>
       </c>
       <c r="L85" t="n">
-        <v>2.72</v>
+        <v>4.82</v>
       </c>
       <c r="M85" t="n">
         <v>0.8</v>
       </c>
       <c r="N85" t="n">
-        <v>0.99</v>
+        <v>2.3</v>
       </c>
       <c r="O85" t="n">
         <v>-1.31</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S85" t="b">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -5322,28 +6353,28 @@
         <v>5.62</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46322.55208333334</v>
+        <v>46323.38541666666</v>
       </c>
       <c r="H86" t="n">
-        <v>1202.1</v>
+        <v>1167.7</v>
       </c>
       <c r="I86" t="n">
         <v>1167.901744850155</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.75</v>
+        <v>-3.59</v>
       </c>
       <c r="L86" t="n">
         <v>3.97</v>
       </c>
       <c r="M86" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="N86" t="n">
-        <v>1.35</v>
+        <v>3.5</v>
       </c>
       <c r="O86" t="n">
         <v>2.3</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>2</v>
+      </c>
+      <c r="U86" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -5403,6 +6446,12 @@
       <c r="Q87" t="n">
         <v>2</v>
       </c>
+      <c r="R87" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7505,7 +8554,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.6</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="6">
@@ -7515,7 +8564,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -7525,7 +8574,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>90.2</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
@@ -7535,7 +8584,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7545,7 +8594,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="10">
@@ -7555,7 +8604,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39.1</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="11">
@@ -7595,7 +8644,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="15">
@@ -7605,7 +8654,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.18</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="16">
@@ -7615,7 +8664,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.01</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="17">
@@ -7625,7 +8674,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.2</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="18">
@@ -7635,7 +8684,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42.4</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="19">
@@ -7645,7 +8694,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="20">
@@ -7655,7 +8704,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.32</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="21">
@@ -7665,7 +8714,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.71</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="22">
@@ -7675,7 +8724,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -7695,7 +8744,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.87</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="25">
@@ -7705,7 +8754,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.43</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="26">
@@ -7715,7 +8764,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.05</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="27">
@@ -7725,7 +8774,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.5</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="28">
@@ -7735,7 +8784,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
